--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/Panel-28/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.8433</v>
+        <v>17.33619</v>
       </c>
       <c r="D2" t="n">
-        <v>16.90818</v>
+        <v>16.7489</v>
       </c>
       <c r="E2" t="n">
-        <v>16.51141</v>
+        <v>16.78974</v>
       </c>
       <c r="F2" t="n">
-        <v>43.5905</v>
+        <v>42.15275</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05132</v>
+        <v>0.05154</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80245</v>
+        <v>1.82952</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.75308</v>
+        <v>17.05913</v>
       </c>
       <c r="D3" t="n">
-        <v>16.75419</v>
+        <v>16.8871</v>
       </c>
       <c r="E3" t="n">
-        <v>16.78401</v>
+        <v>17.0521</v>
       </c>
       <c r="F3" t="n">
-        <v>42.59362</v>
+        <v>43.36669</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05089</v>
+        <v>0.05164</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84533</v>
+        <v>1.8915</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.89573</v>
+        <v>17.05204</v>
       </c>
       <c r="D4" t="n">
-        <v>16.45798</v>
+        <v>16.74874</v>
       </c>
       <c r="E4" t="n">
-        <v>16.74627</v>
+        <v>16.92233</v>
       </c>
       <c r="F4" t="n">
-        <v>41.72625</v>
+        <v>42.77611</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05041</v>
+        <v>0.05064</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82942</v>
+        <v>1.82707</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.78689</v>
+        <v>17.15933</v>
       </c>
       <c r="D5" t="n">
-        <v>16.88564</v>
+        <v>16.44956</v>
       </c>
       <c r="E5" t="n">
-        <v>16.98617</v>
+        <v>16.89769</v>
       </c>
       <c r="F5" t="n">
-        <v>43.25094</v>
+        <v>42.28017</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04964</v>
+        <v>0.05175</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81501</v>
+        <v>1.8408</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +559,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>17.06927</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.83866</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.87211</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41.30815</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05089</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.83521</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.08122</v>
+        <v>17.06507</v>
       </c>
       <c r="D7" t="n">
-        <v>16.85473</v>
+        <v>16.81032</v>
       </c>
       <c r="E7" t="n">
-        <v>16.54693</v>
+        <v>16.82721</v>
       </c>
       <c r="F7" t="n">
-        <v>42.56776</v>
+        <v>42.41222</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05054</v>
+        <v>0.05126</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85017</v>
+        <v>1.84562</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.12054</v>
+        <v>17.02523</v>
       </c>
       <c r="D8" t="n">
-        <v>16.82863</v>
+        <v>16.66098</v>
       </c>
       <c r="E8" t="n">
-        <v>17.02834</v>
+        <v>16.73854</v>
       </c>
       <c r="F8" t="n">
-        <v>43.44541</v>
+        <v>42.13354</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05077</v>
+        <v>0.05158</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84934</v>
+        <v>1.8056</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.02129</v>
+        <v>17.33418</v>
       </c>
       <c r="D9" t="n">
-        <v>16.90187</v>
+        <v>16.45733</v>
       </c>
       <c r="E9" t="n">
-        <v>16.85906</v>
+        <v>17.06849</v>
       </c>
       <c r="F9" t="n">
-        <v>43.79451</v>
+        <v>42.49891</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05093</v>
+        <v>0.05226</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83815</v>
+        <v>1.7873</v>
       </c>
     </row>
     <row r="10">
@@ -647,583 +660,712 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.73788</v>
+        <v>16.92055</v>
       </c>
       <c r="D10" t="n">
-        <v>16.49428</v>
+        <v>16.87094</v>
       </c>
       <c r="E10" t="n">
-        <v>16.8071</v>
+        <v>16.89909</v>
       </c>
       <c r="F10" t="n">
-        <v>42.22349</v>
+        <v>42.6295</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05188</v>
+        <v>0.05042</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8297</v>
+        <v>1.80262</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.7683</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.45454</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.75649</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.13695</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05068</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.86083</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.87255</v>
+        <v>17.06343</v>
       </c>
       <c r="D12" t="n">
-        <v>16.46903</v>
+        <v>16.44416</v>
       </c>
       <c r="E12" t="n">
-        <v>16.58412</v>
+        <v>16.99437</v>
       </c>
       <c r="F12" t="n">
-        <v>21.94201</v>
+        <v>42.02225</v>
       </c>
       <c r="G12" t="n">
-        <v>34.83485</v>
+        <v>0.05127</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8204</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.91484</v>
+        <v>16.73768</v>
       </c>
       <c r="D13" t="n">
-        <v>16.01567</v>
+        <v>16.67968</v>
       </c>
       <c r="E13" t="n">
-        <v>16.12327</v>
+        <v>16.7265</v>
       </c>
       <c r="F13" t="n">
-        <v>21.28449</v>
+        <v>42.80323</v>
       </c>
       <c r="G13" t="n">
-        <v>35.12537</v>
+        <v>0.05159</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.84238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.1468</v>
+        <v>17.20248</v>
       </c>
       <c r="D14" t="n">
-        <v>16.34105</v>
+        <v>16.6035</v>
       </c>
       <c r="E14" t="n">
-        <v>16.53447</v>
+        <v>16.60633</v>
       </c>
       <c r="F14" t="n">
-        <v>21.99919</v>
+        <v>42.70481</v>
       </c>
       <c r="G14" t="n">
-        <v>34.20129</v>
+        <v>0.05184</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.87094</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.56923</v>
+        <v>16.94449</v>
       </c>
       <c r="D15" t="n">
-        <v>16.25568</v>
+        <v>16.60087</v>
       </c>
       <c r="E15" t="n">
-        <v>16.6049</v>
+        <v>16.82287</v>
       </c>
       <c r="F15" t="n">
-        <v>21.71465</v>
+        <v>42.58999</v>
       </c>
       <c r="G15" t="n">
-        <v>34.41831</v>
+        <v>0.05165</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.85136</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.77385</v>
+        <v>17.00732</v>
       </c>
       <c r="D16" t="n">
-        <v>15.84633</v>
+        <v>16.38101</v>
       </c>
       <c r="E16" t="n">
-        <v>16.12895</v>
+        <v>16.91753</v>
       </c>
       <c r="F16" t="n">
-        <v>21.58344</v>
+        <v>41.93739</v>
       </c>
       <c r="G16" t="n">
-        <v>35.13966</v>
+        <v>0.05015</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.85435</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.88226</v>
+        <v>16.98817</v>
       </c>
       <c r="D17" t="n">
-        <v>15.93863</v>
+        <v>16.76307</v>
       </c>
       <c r="E17" t="n">
-        <v>16.3841</v>
+        <v>16.94166</v>
       </c>
       <c r="F17" t="n">
-        <v>21.8025</v>
+        <v>42.25532</v>
       </c>
       <c r="G17" t="n">
-        <v>34.87806</v>
+        <v>0.05108</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83275</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.55636</v>
+        <v>16.81279</v>
       </c>
       <c r="D18" t="n">
-        <v>16.10345</v>
+        <v>16.61633</v>
       </c>
       <c r="E18" t="n">
-        <v>16.67789</v>
+        <v>16.64251</v>
       </c>
       <c r="F18" t="n">
-        <v>22.11258</v>
+        <v>43.06736</v>
       </c>
       <c r="G18" t="n">
-        <v>34.71293</v>
+        <v>0.05213</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84417</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.58561</v>
+        <v>16.98862</v>
       </c>
       <c r="D19" t="n">
-        <v>16.16039</v>
+        <v>16.67206</v>
       </c>
       <c r="E19" t="n">
-        <v>16.58452</v>
+        <v>16.70637</v>
       </c>
       <c r="F19" t="n">
-        <v>21.76197</v>
+        <v>42.64909</v>
       </c>
       <c r="G19" t="n">
-        <v>34.53321</v>
+        <v>0.05105</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.85946</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>16.59601</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.26967</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.23169</v>
-      </c>
-      <c r="F20" t="n">
-        <v>21.7355</v>
-      </c>
-      <c r="G20" t="n">
-        <v>34.08935</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6091299999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.13071</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.75434</v>
+        <v>0.60932</v>
       </c>
       <c r="D22" t="n">
-        <v>0.07953</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.60182</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.97624</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.11081</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09238</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12772</v>
+        <v>1.1215</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.75945</v>
+        <v>0.608</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07998</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.61661</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.96735</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.11093</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09266000000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12856</v>
+        <v>1.13794</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75</v>
+        <v>0.59592</v>
       </c>
       <c r="D24" t="n">
-        <v>0.07965</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.59688</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.9661999999999999</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.11167</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00769</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09376</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12926</v>
+        <v>1.10925</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75905</v>
+        <v>0.602</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08097</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.6131799999999999</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.97423</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.11191</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09462</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12868</v>
+        <v>1.11026</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7503</v>
+        <v>0.61776</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08153000000000001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.61632</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.96848</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11009</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09291000000000001</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12881</v>
+        <v>1.12081</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.75161</v>
+        <v>0.60156</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08316999999999999</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.59359</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.96944</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.10958</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09389</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.127</v>
+        <v>1.11756</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.75099</v>
+        <v>0.60219</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08146</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.60863</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.97222</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.10857</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09511</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12389</v>
+        <v>1.10454</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.60606</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.10336</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.75642</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.07951</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.5956900000000001</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.9809099999999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.11013</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09311999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12804</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.76779</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08097</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.61059</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.97141</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.11128</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09474</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12861</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.74743</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08251</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.60772</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.00309</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.10873</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09395000000000001</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12865</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.75575</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08186</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6056</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.95679</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.10864</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09390999999999999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.1308</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.76592</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08287</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.59681</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.96634</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10911</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00748</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09497</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12855</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.76479</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08276</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.61045</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9711</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10861</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09415</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12632</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.75504</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08203000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.62286</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.95133</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.10934</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00767</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09297999999999999</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12629</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.74891</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.08162</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.6045700000000001</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.96085</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.10868</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00769</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09342</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12543</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="C38" t="n">
+        <v>0.74146</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08122</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.60386</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.98392</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11035</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09536</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12755</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.74349</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0814</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.6140099999999999</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.97127</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.11121</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="C39" t="n">
+        <v>0.75124</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6071299999999999</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.96129</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.11162</v>
+      </c>
+      <c r="H39" t="n">
         <v>0.00763</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.09386</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12554</v>
+      <c r="I39" t="n">
+        <v>0.09471</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12582</v>
       </c>
     </row>
   </sheetData>
